--- a/artfynd/A 47725-2024 artfynd.xlsx
+++ b/artfynd/A 47725-2024 artfynd.xlsx
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120785767</v>
+        <v>120785732</v>
       </c>
       <c r="B6" t="n">
         <v>98071</v>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>718710</v>
+        <v>718698</v>
       </c>
       <c r="R6" t="n">
-        <v>7215565</v>
+        <v>7215610</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120785732</v>
+        <v>120785767</v>
       </c>
       <c r="B7" t="n">
         <v>98071</v>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>718698</v>
+        <v>718710</v>
       </c>
       <c r="R7" t="n">
-        <v>7215610</v>
+        <v>7215565</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -2491,10 +2491,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120785814</v>
+        <v>120785716</v>
       </c>
       <c r="B19" t="n">
-        <v>74705</v>
+        <v>98071</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2503,30 +2503,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2534,10 +2535,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>718741</v>
+        <v>718685</v>
       </c>
       <c r="R19" t="n">
-        <v>7215541</v>
+        <v>7215600</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2597,10 +2598,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120786040</v>
+        <v>120786347</v>
       </c>
       <c r="B20" t="n">
-        <v>105161</v>
+        <v>98071</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2609,25 +2610,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2641,10 +2642,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>718970</v>
+        <v>718877</v>
       </c>
       <c r="R20" t="n">
-        <v>7215504</v>
+        <v>7215527</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2704,10 +2705,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120785716</v>
+        <v>120786040</v>
       </c>
       <c r="B21" t="n">
-        <v>98071</v>
+        <v>105161</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2716,25 +2717,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,10 +2749,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>718685</v>
+        <v>718970</v>
       </c>
       <c r="R21" t="n">
-        <v>7215600</v>
+        <v>7215504</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2811,10 +2812,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120786347</v>
+        <v>120785986</v>
       </c>
       <c r="B22" t="n">
-        <v>98071</v>
+        <v>79714</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2823,31 +2824,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>718877</v>
+        <v>718856</v>
       </c>
       <c r="R22" t="n">
-        <v>7215527</v>
+        <v>7215536</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120785986</v>
+        <v>120785814</v>
       </c>
       <c r="B23" t="n">
-        <v>79714</v>
+        <v>74705</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2930,25 +2930,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>718856</v>
+        <v>718741</v>
       </c>
       <c r="R23" t="n">
-        <v>7215536</v>
+        <v>7215541</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3024,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120785953</v>
+        <v>120785785</v>
       </c>
       <c r="B24" t="n">
-        <v>98071</v>
+        <v>82382</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3036,31 +3036,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3068,10 +3067,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>718763</v>
+        <v>718720</v>
       </c>
       <c r="R24" t="n">
-        <v>7215574</v>
+        <v>7215571</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3131,7 +3130,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120785735</v>
+        <v>120785953</v>
       </c>
       <c r="B25" t="n">
         <v>98071</v>
@@ -3175,10 +3174,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>718710</v>
+        <v>718763</v>
       </c>
       <c r="R25" t="n">
-        <v>7215580</v>
+        <v>7215574</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3238,10 +3237,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120785785</v>
+        <v>120785735</v>
       </c>
       <c r="B26" t="n">
-        <v>82382</v>
+        <v>98071</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3250,30 +3249,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>718720</v>
+        <v>718710</v>
       </c>
       <c r="R26" t="n">
-        <v>7215571</v>
+        <v>7215580</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
